--- a/public/post/drafts/season-prediction/men_model-exhaustive-tests-predicted_mae.xlsx
+++ b/public/post/drafts/season-prediction/men_model-exhaustive-tests-predicted_mae.xlsx
@@ -561,25 +561,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>0.113695568010199</v>
+        <v>0.112990342472339</v>
       </c>
       <c r="C7" t="n">
-        <v>0.124912214889581</v>
+        <v>0.124114106733776</v>
       </c>
       <c r="D7" t="n">
-        <v>0.162917480932318</v>
+        <v>0.162112249601465</v>
       </c>
       <c r="E7" t="n">
-        <v>0.118637157651092</v>
+        <v>0.118304927973073</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0910461207278854</v>
+        <v>0.0930289169863382</v>
       </c>
       <c r="G7" t="n">
-        <v>0.12797389769245</v>
+        <v>0.125047472607934</v>
       </c>
       <c r="H7" t="n">
-        <v>0.123197073317254</v>
+        <v>0.122599669395821</v>
       </c>
     </row>
     <row r="8">
